--- a/data/CPI-India.xlsx
+++ b/data/CPI-India.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iimv1-my.sharepoint.com/personal/kalyan_iimv_ac_in/Documents/Kalyan-Research/APO/Data-Analysis-Manuscript/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e46a4301436fbcaf/Kalyan/KK-Python/Kalyan-Jupyter-Notebooks/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{C3FBF667-0E22-AF45-A263-2823825697C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A893936-DE78-3B4C-BAFE-8CDE23C5D234}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{C3FBF667-0E22-AF45-A263-2823825697C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0656EA38-7439-3F40-8332-343014C88185}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10220" yWindow="1460" windowWidth="27640" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPI-YoY" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="CPI-Weights" sheetId="3" r:id="rId4"/>
     <sheet name="Core-NonCore-CPI" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -714,9 +714,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -754,7 +754,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -860,7 +860,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1002,7 +1002,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4024,6 +4024,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">

--- a/data/CPI-India.xlsx
+++ b/data/CPI-India.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="81" documentId="8_{C3FBF667-0E22-AF45-A263-2823825697C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0656EA38-7439-3F40-8332-343014C88185}"/>
   <bookViews>
-    <workbookView xWindow="10220" yWindow="1460" windowWidth="27640" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1680" yWindow="1260" windowWidth="27640" windowHeight="15100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CPI-YoY" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="CPI-Weights" sheetId="3" r:id="rId4"/>
     <sheet name="Core-NonCore-CPI" sheetId="4" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
